--- a/BVSimulationFiles/93.xlsx
+++ b/BVSimulationFiles/93.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0005161290322580645</v>
+        <v>0.001032258064516129</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004927875137424688</v>
+        <v>0.0009855750274849375</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004703530148957671</v>
+        <v>0.0009407060297915342</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004488029974071644</v>
+        <v>0.0008976059948143288</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004281142182187546</v>
+        <v>0.0008562284364375092</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004082629043558053</v>
+        <v>0.0008165258087116106</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003892249087370328</v>
+        <v>0.0007784498174740656</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003709758486544226</v>
+        <v>0.0007419516973088452</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000353491228475562</v>
+        <v>0.000706982456951124</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0003367465479953218</v>
+        <v>0.0006734930959906437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003207173977472737</v>
+        <v>0.0006414347954945474</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003053795424777429</v>
+        <v>0.0006107590849554858</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0002907089938862183</v>
+        <v>0.0005814179877724366</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0002766820736443353</v>
+        <v>0.0005533641472886706</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0002632754676212663</v>
+        <v>0.0005265509352425326</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002504662721655446</v>
+        <v>0.0005009325443310891</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0002382320332216291</v>
+        <v>0.0004764640664432582</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002265507789934378</v>
+        <v>0.0004531015579868756</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0002154010468061977</v>
+        <v>0.0004308020936123954</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0002047619047619047</v>
+        <v>0.0004095238095238094</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0005161290322580645</v>
+        <v>0.001032258064516129</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004927875137424688</v>
+        <v>0.0009855750274849375</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004703530148957671</v>
+        <v>0.0009407060297915342</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004488029974071644</v>
+        <v>0.0008976059948143288</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004281142182187546</v>
+        <v>0.0008562284364375092</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004082629043558053</v>
+        <v>0.0008165258087116106</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0003892249087370328</v>
+        <v>0.0007784498174740656</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003709758486544226</v>
+        <v>0.0007419516973088452</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000353491228475562</v>
+        <v>0.000706982456951124</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003367465479953218</v>
+        <v>0.0006734930959906437</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003207173977472737</v>
+        <v>0.0006414347954945474</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003053795424777429</v>
+        <v>0.0006107590849554858</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0002907089938862183</v>
+        <v>0.0005814179877724366</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0002766820736443353</v>
+        <v>0.0005533641472886706</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0002632754676212663</v>
+        <v>0.0005265509352425326</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002504662721655446</v>
+        <v>0.0005009325443310891</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002382320332216291</v>
+        <v>0.0004764640664432582</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002265507789934378</v>
+        <v>0.0004531015579868756</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0002154010468061977</v>
+        <v>0.0004308020936123954</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0002047619047619047</v>
+        <v>0.0004095238095238094</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/93.xlsx
+++ b/BVSimulationFiles/93.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001032258064516129</v>
+        <v>0.01032258064516129</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009855750274849375</v>
+        <v>0.009855750274849376</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009407060297915342</v>
+        <v>0.009407060297915342</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008976059948143288</v>
+        <v>0.008976059948143288</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008562284364375092</v>
+        <v>0.008562284364375092</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008165258087116106</v>
+        <v>0.008165258087116106</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007784498174740656</v>
+        <v>0.007784498174740656</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007419516973088452</v>
+        <v>0.007419516973088453</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000706982456951124</v>
+        <v>0.007069824569511239</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0006734930959906437</v>
+        <v>0.006734930959906437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006414347954945474</v>
+        <v>0.006414347954945474</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0006107590849554858</v>
+        <v>0.006107590849554858</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0005814179877724366</v>
+        <v>0.005814179877724366</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0005533641472886706</v>
+        <v>0.005533641472886706</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0005265509352425326</v>
+        <v>0.005265509352425326</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0005009325443310891</v>
+        <v>0.005009325443310892</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0004764640664432582</v>
+        <v>0.004764640664432582</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004531015579868756</v>
+        <v>0.004531015579868756</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0004308020936123954</v>
+        <v>0.004308020936123954</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0004095238095238094</v>
+        <v>0.004095238095238094</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001032258064516129</v>
+        <v>0.01032258064516129</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009855750274849375</v>
+        <v>0.009855750274849376</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009407060297915342</v>
+        <v>0.009407060297915342</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008976059948143288</v>
+        <v>0.008976059948143288</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008562284364375092</v>
+        <v>0.008562284364375092</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008165258087116106</v>
+        <v>0.008165258087116106</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007784498174740656</v>
+        <v>0.007784498174740656</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007419516973088452</v>
+        <v>0.007419516973088453</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000706982456951124</v>
+        <v>0.007069824569511239</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006734930959906437</v>
+        <v>0.006734930959906437</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006414347954945474</v>
+        <v>0.006414347954945474</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006107590849554858</v>
+        <v>0.006107590849554858</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0005814179877724366</v>
+        <v>0.005814179877724366</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0005533641472886706</v>
+        <v>0.005533641472886706</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005265509352425326</v>
+        <v>0.005265509352425326</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0005009325443310891</v>
+        <v>0.005009325443310892</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004764640664432582</v>
+        <v>0.004764640664432582</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004531015579868756</v>
+        <v>0.004531015579868756</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004308020936123954</v>
+        <v>0.004308020936123954</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004095238095238094</v>
+        <v>0.004095238095238094</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/93.xlsx
+++ b/BVSimulationFiles/93.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,61 +421,16 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.03725894736842105</v>
+        <v>0.02441103448275862</v>
       </c>
       <c r="D1" t="n">
-        <v>0.0745178947368421</v>
+        <v>0.04882206896551725</v>
       </c>
       <c r="E1" t="n">
-        <v>0.1117768421052632</v>
+        <v>0.07323310344827587</v>
       </c>
       <c r="F1" t="n">
-        <v>0.1490357894736842</v>
-      </c>
-      <c r="G1" t="n">
-        <v>0.1862947368421053</v>
-      </c>
-      <c r="H1" t="n">
-        <v>0.2235536842105263</v>
-      </c>
-      <c r="I1" t="n">
-        <v>0.2608126315789474</v>
-      </c>
-      <c r="J1" t="n">
-        <v>0.2980715789473684</v>
-      </c>
-      <c r="K1" t="n">
-        <v>0.3353305263157895</v>
-      </c>
-      <c r="L1" t="n">
-        <v>0.3725894736842105</v>
-      </c>
-      <c r="M1" t="n">
-        <v>0.4098484210526316</v>
-      </c>
-      <c r="N1" t="n">
-        <v>0.4471073684210526</v>
-      </c>
-      <c r="O1" t="n">
-        <v>0.4843663157894737</v>
-      </c>
-      <c r="P1" t="n">
-        <v>0.5216252631578948</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>0.5588842105263158</v>
-      </c>
-      <c r="R1" t="n">
-        <v>0.5961431578947368</v>
-      </c>
-      <c r="S1" t="n">
-        <v>0.633402105263158</v>
-      </c>
-      <c r="T1" t="n">
-        <v>0.6706610526315789</v>
-      </c>
-      <c r="U1" t="n">
-        <v>0.70792</v>
+        <v>0.09764413793103449</v>
       </c>
     </row>
     <row r="2">
@@ -483,64 +438,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01032258064516129</v>
+        <v>0.03233857326777755</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009855750274849376</v>
+        <v>0.03228388943621345</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009407060297915342</v>
+        <v>0.03202745836227791</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008976059948143288</v>
+        <v>0.03160219564331144</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008562284364375092</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.008165258087116106</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.007784498174740656</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.007419516973088453</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.007069824569511239</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.006734930959906437</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.006414347954945474</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.006107590849554858</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.005814179877724366</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.005533641472886706</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.005265509352425326</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.005009325443310892</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.004764640664432582</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.004531015579868756</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.004308020936123954</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.004095238095238094</v>
+        <v>0.03103701838073242</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +458,19 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01032258064516129</v>
+        <v>0.03233857326777755</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009855750274849376</v>
+        <v>0.03228388943621345</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009407060297915342</v>
+        <v>0.03202745836227791</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008976059948143288</v>
+        <v>0.03160219564331144</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008562284364375092</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.008165258087116106</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.007784498174740656</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.007419516973088453</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.007069824569511239</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.006734930959906437</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.006414347954945474</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.006107590849554858</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.005814179877724366</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.005533641472886706</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.005265509352425326</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.005009325443310892</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.004764640664432582</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.004531015579868756</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.004308020936123954</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.004095238095238094</v>
+        <v>0.03103701838073242</v>
       </c>
     </row>
   </sheetData>
